--- a/data-source/可升级建筑数据.xlsx
+++ b/data-source/可升级建筑数据.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasonX\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC89C3D-B236-4B7A-AA87-CE08E606C428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A2922B-B5D7-42A3-998B-7B86D1DC67F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9A7D2943-CAC0-4F21-9EB5-FAC98526D314}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="162">
   <si>
     <t>建筑名称</t>
   </si>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t>地球仪*1；干净的羊皮纸*30；松木板*40；铜锭*20；皮革*10；线*5；绳子*20；布料*20</t>
+  </si>
+  <si>
+    <t>非城堡建筑</t>
   </si>
 </sst>
 </file>
@@ -764,11 +767,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1155,7 +1158,7 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="6">
@@ -1187,7 +1190,7 @@
       <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="27" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
+      <c r="A3" s="8"/>
       <c r="B3" s="6"/>
       <c r="C3" s="3" t="s">
         <v>76</v>
@@ -1201,7 +1204,7 @@
       <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H3" s="6"/>
@@ -1213,7 +1216,7 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="6"/>
       <c r="C4" s="3" t="s">
         <v>77</v>
@@ -1227,7 +1230,7 @@
       <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="8"/>
+      <c r="G4" s="7"/>
       <c r="H4" s="6"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1237,7 +1240,7 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="6"/>
       <c r="C5" s="3" t="s">
         <v>78</v>
@@ -1251,7 +1254,7 @@
       <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="8"/>
+      <c r="G5" s="7"/>
       <c r="H5" s="6"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -1261,7 +1264,7 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="6">
@@ -1293,7 +1296,7 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="6"/>
       <c r="C7" s="3" t="s">
         <v>76</v>
@@ -1307,7 +1310,7 @@
       <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H7" s="6"/>
@@ -1319,7 +1322,7 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="6"/>
       <c r="C8" s="3" t="s">
         <v>77</v>
@@ -1333,7 +1336,7 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="8"/>
+      <c r="G8" s="7"/>
       <c r="H8" s="6"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1343,7 +1346,7 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
+      <c r="A9" s="8"/>
       <c r="B9" s="6"/>
       <c r="C9" s="3" t="s">
         <v>78</v>
@@ -1357,7 +1360,7 @@
       <c r="F9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="8"/>
+      <c r="G9" s="7"/>
       <c r="H9" s="6"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1367,7 +1370,7 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="6">
@@ -1399,7 +1402,7 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
+      <c r="A11" s="8"/>
       <c r="B11" s="6"/>
       <c r="C11" s="3" t="s">
         <v>76</v>
@@ -1413,7 +1416,7 @@
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H11" s="6"/>
@@ -1425,7 +1428,7 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="6"/>
       <c r="C12" s="3" t="s">
         <v>77</v>
@@ -1439,7 +1442,7 @@
       <c r="F12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="8"/>
+      <c r="G12" s="7"/>
       <c r="H12" s="6"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1449,7 +1452,7 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="6"/>
       <c r="C13" s="3" t="s">
         <v>78</v>
@@ -1463,7 +1466,7 @@
       <c r="F13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="8"/>
+      <c r="G13" s="7"/>
       <c r="H13" s="6"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1473,7 +1476,7 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="6">
@@ -1505,7 +1508,7 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
+      <c r="A15" s="8"/>
       <c r="B15" s="6"/>
       <c r="C15" s="3" t="s">
         <v>76</v>
@@ -1519,7 +1522,7 @@
       <c r="F15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H15" s="6"/>
@@ -1531,7 +1534,7 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="6"/>
       <c r="C16" s="3" t="s">
         <v>77</v>
@@ -1545,7 +1548,7 @@
       <c r="F16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="8"/>
+      <c r="G16" s="7"/>
       <c r="H16" s="6"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1555,7 +1558,7 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="6"/>
       <c r="C17" s="3" t="s">
         <v>78</v>
@@ -1569,7 +1572,7 @@
       <c r="F17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="8"/>
+      <c r="G17" s="7"/>
       <c r="H17" s="6"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1579,7 +1582,7 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="6">
@@ -1611,7 +1614,7 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="6"/>
       <c r="C19" s="3" t="s">
         <v>76</v>
@@ -1625,7 +1628,7 @@
       <c r="F19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H19" s="6"/>
@@ -1637,7 +1640,7 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
+      <c r="A20" s="8"/>
       <c r="B20" s="6"/>
       <c r="C20" s="3" t="s">
         <v>77</v>
@@ -1651,7 +1654,7 @@
       <c r="F20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="8"/>
+      <c r="G20" s="7"/>
       <c r="H20" s="6"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1661,7 +1664,7 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
+      <c r="A21" s="8"/>
       <c r="B21" s="6"/>
       <c r="C21" s="3" t="s">
         <v>78</v>
@@ -1675,7 +1678,7 @@
       <c r="F21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="8"/>
+      <c r="G21" s="7"/>
       <c r="H21" s="6"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1737,7 +1740,7 @@
         <v>54</v>
       </c>
       <c r="H23" s="6"/>
-      <c r="I23" s="8"/>
+      <c r="I23" s="7"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1763,7 +1766,7 @@
         <v>54</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="8"/>
+      <c r="I24" s="7"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1789,7 +1792,7 @@
         <v>57</v>
       </c>
       <c r="H25" s="6"/>
-      <c r="I25" s="8"/>
+      <c r="I25" s="7"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1849,7 +1852,7 @@
         <v>64</v>
       </c>
       <c r="H27" s="6"/>
-      <c r="I27" s="8"/>
+      <c r="I27" s="7"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1875,7 +1878,7 @@
         <v>64</v>
       </c>
       <c r="H28" s="6"/>
-      <c r="I28" s="8"/>
+      <c r="I28" s="7"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1901,7 +1904,7 @@
         <v>57</v>
       </c>
       <c r="H29" s="6"/>
-      <c r="I29" s="8"/>
+      <c r="I29" s="7"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -2511,7 +2514,7 @@
       <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B58" s="6">
@@ -2538,7 +2541,7 @@
       <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A59" s="7"/>
+      <c r="A59" s="8"/>
       <c r="B59" s="6"/>
       <c r="C59" s="3" t="s">
         <v>75</v>
@@ -2559,7 +2562,7 @@
       <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A60" s="7"/>
+      <c r="A60" s="8"/>
       <c r="B60" s="6"/>
       <c r="C60" s="3" t="s">
         <v>76</v>
@@ -2580,7 +2583,7 @@
       <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A61" s="7"/>
+      <c r="A61" s="8"/>
       <c r="B61" s="6"/>
       <c r="C61" s="3" t="s">
         <v>77</v>
@@ -2601,7 +2604,7 @@
       <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A62" s="7"/>
+      <c r="A62" s="8"/>
       <c r="B62" s="6"/>
       <c r="C62" s="3" t="s">
         <v>78</v>
@@ -2728,7 +2731,7 @@
       <c r="A68" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>156</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -2747,13 +2750,13 @@
         <v>157</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
-      <c r="B69" s="8"/>
+      <c r="B69" s="7"/>
       <c r="C69" s="3" t="s">
         <v>76</v>
       </c>
@@ -2772,7 +2775,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
-      <c r="B70" s="8"/>
+      <c r="B70" s="7"/>
       <c r="C70" s="3" t="s">
         <v>77</v>
       </c>
@@ -2791,7 +2794,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
-      <c r="B71" s="8"/>
+      <c r="B71" s="7"/>
       <c r="C71" s="3" t="s">
         <v>78</v>
       </c>
@@ -2813,6 +2816,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="I22:I25"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="I26:I29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="B53:B57"/>
+    <mergeCell ref="G48:G52"/>
+    <mergeCell ref="G53:G57"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="G30:G33"/>
+    <mergeCell ref="B30:B33"/>
     <mergeCell ref="A68:A71"/>
     <mergeCell ref="B68:B71"/>
     <mergeCell ref="D68:D71"/>
@@ -2829,50 +2876,6 @@
     <mergeCell ref="A48:A52"/>
     <mergeCell ref="A53:A57"/>
     <mergeCell ref="B48:B52"/>
-    <mergeCell ref="B53:B57"/>
-    <mergeCell ref="G48:G52"/>
-    <mergeCell ref="G53:G57"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="G30:G33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="H39:H42"/>
-    <mergeCell ref="I22:I25"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="I26:I29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B6:B9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
